--- a/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{998538DC-9FE1-427E-9DA7-643B0749B752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{941E440A-AABE-4B09-8816-DDAF799EDCF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -777,13 +777,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH03,S01aH04,S03aH04,S02aH02,S04aH03,S03aH02,S01aH05,S01aH03,S02aH03,S04aH05,S01aH02,S04aH04,S03aH05,S02aH04,S02aH05,S04aH02</t>
+    <t>S01aH05,S03aH04,S04aH03,S01aH03,S01aH02,S04aH04,S03aH05,S01aH04,S03aH02,S03aH03,S02aH04,S02aH05,S02aH03,S04aH02,S04aH05,S02aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S02aH06,S01aH06</t>
+    <t>S02aH01,S01aH06,S03aH06,S02aH06,S01aH01,S04aH01,S04aH06,S03aH01</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S02aH06,S01aH06</v>
+        <v>S02aH01,S01aH06,S03aH06,S02aH06,S01aH01,S04aH01,S04aH06,S03aH01</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH03,S01aH04,S03aH04,S02aH02,S04aH03,S03aH02,S01aH05,S01aH03,S02aH03,S04aH05,S01aH02,S04aH04,S03aH05,S02aH04,S02aH05,S04aH02</v>
+        <v>S01aH05,S03aH04,S04aH03,S01aH03,S01aH02,S04aH04,S03aH05,S01aH04,S03aH02,S03aH03,S02aH04,S02aH05,S02aH03,S04aH02,S04aH05,S02aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1506,7 +1506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD048C4-175F-4121-A7B2-FBB0F77EF773}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED269824-4EA6-4F57-856B-BD61673B26F0}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1612,7 +1612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EB4539E-1B80-4926-83F7-E7BBB37501D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D8CD89-7382-4E2F-8CC9-E585F13603C7}">
   <dimension ref="B9:O826"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25194,7 +25194,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A23EB1BE-E781-4327-83A8-38D129A66573}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C95237-FCD9-43AD-B3B8-C87D3BF56ADE}">
   <dimension ref="B9:DH86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38709,7 +38709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC3490-CEDD-4D87-8377-B9B39C825870}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CC4540-52D1-49C2-A2E4-D47B22EC8900}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39075,7 +39075,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E5BBF2-D35D-4D23-9D3F-B6AA2D821EE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA1BD46D-E2AE-4493-9196-7D252043C929}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39630,7 +39630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7856119D-2891-4E96-9E2B-0C5C06EFEC78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD64844-680E-4572-92FB-CF1D71A93647}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39921,7 +39921,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9326E1D5-CBC0-4547-9EA9-4B545D87E852}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1040F9-753A-41B2-97FF-FDF7DC1F0E8E}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40009,7 +40009,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.21483333333333332</v>
+        <v>0.21483333333333335</v>
       </c>
       <c r="E15" t="s">
         <v>253</v>
@@ -40065,7 +40065,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.23490000000000003</v>
+        <v>0.2349</v>
       </c>
       <c r="E19" t="s">
         <v>253</v>
@@ -40233,7 +40233,7 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>0.46616666666666667</v>
+        <v>0.46616666666666662</v>
       </c>
       <c r="E31" t="s">
         <v>253</v>
@@ -40275,7 +40275,7 @@
         <v>45</v>
       </c>
       <c r="D34">
-        <v>0.37133333333333335</v>
+        <v>0.37133333333333329</v>
       </c>
       <c r="E34" t="s">
         <v>253</v>
@@ -40359,7 +40359,7 @@
         <v>41</v>
       </c>
       <c r="D40">
-        <v>0.30979999999999996</v>
+        <v>0.30980000000000002</v>
       </c>
       <c r="E40" t="s">
         <v>253</v>
@@ -40457,7 +40457,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.41359999999999997</v>
+        <v>0.41360000000000002</v>
       </c>
       <c r="E47" t="s">
         <v>253</v>
@@ -40611,7 +40611,7 @@
         <v>45</v>
       </c>
       <c r="D58">
-        <v>0.29836666666666672</v>
+        <v>0.29836666666666667</v>
       </c>
       <c r="E58" t="s">
         <v>253</v>
@@ -40625,7 +40625,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.39840000000000003</v>
+        <v>0.39839999999999992</v>
       </c>
       <c r="E59" t="s">
         <v>253</v>
@@ -40695,7 +40695,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.2044</v>
+        <v>0.20440000000000003</v>
       </c>
       <c r="E64" t="s">
         <v>253</v>
@@ -40723,7 +40723,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.27663333333333334</v>
+        <v>0.27663333333333329</v>
       </c>
       <c r="E66" t="s">
         <v>253</v>
@@ -40821,7 +40821,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.1618333333333333</v>
+        <v>0.16183333333333336</v>
       </c>
       <c r="E73" t="s">
         <v>253</v>
@@ -40975,7 +40975,7 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <v>0.19736666666666666</v>
+        <v>0.19736666666666669</v>
       </c>
       <c r="E84" t="s">
         <v>253</v>
@@ -40989,7 +40989,7 @@
         <v>43</v>
       </c>
       <c r="D85">
-        <v>0.16566666666666666</v>
+        <v>0.16566666666666668</v>
       </c>
       <c r="E85" t="s">
         <v>253</v>
@@ -41017,7 +41017,7 @@
         <v>37</v>
       </c>
       <c r="D87">
-        <v>0.42363333333333336</v>
+        <v>0.42363333333333331</v>
       </c>
       <c r="E87" t="s">
         <v>253</v>
@@ -41045,7 +41045,7 @@
         <v>43</v>
       </c>
       <c r="D89">
-        <v>0.21050000000000002</v>
+        <v>0.21049999999999999</v>
       </c>
       <c r="E89" t="s">
         <v>253</v>
@@ -41101,7 +41101,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.17826666666666666</v>
+        <v>0.17826666666666668</v>
       </c>
       <c r="E93" t="s">
         <v>253</v>
@@ -41115,7 +41115,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.33363333333333328</v>
+        <v>0.33363333333333339</v>
       </c>
       <c r="E94" t="s">
         <v>253</v>
@@ -41241,7 +41241,7 @@
         <v>37</v>
       </c>
       <c r="D103">
-        <v>0.47876666666666662</v>
+        <v>0.47876666666666673</v>
       </c>
       <c r="E103" t="s">
         <v>253</v>
@@ -41297,7 +41297,7 @@
         <v>37</v>
       </c>
       <c r="D107">
-        <v>0.4017</v>
+        <v>0.40169999999999995</v>
       </c>
       <c r="E107" t="s">
         <v>253</v>
@@ -41339,7 +41339,7 @@
         <v>45</v>
       </c>
       <c r="D110">
-        <v>0.26300000000000001</v>
+        <v>0.26299999999999996</v>
       </c>
       <c r="E110" t="s">
         <v>253</v>
@@ -41353,7 +41353,7 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.45990000000000003</v>
+        <v>0.45989999999999998</v>
       </c>
       <c r="E111" t="s">
         <v>253</v>
@@ -41367,7 +41367,7 @@
         <v>41</v>
       </c>
       <c r="D112">
-        <v>0.2659333333333333</v>
+        <v>0.26593333333333335</v>
       </c>
       <c r="E112" t="s">
         <v>253</v>
@@ -41479,7 +41479,7 @@
         <v>41</v>
       </c>
       <c r="D120">
-        <v>0.30656666666666671</v>
+        <v>0.30656666666666665</v>
       </c>
       <c r="E120" t="s">
         <v>253</v>
